--- a/Excel Class Files/Part 8 What if Analysis.xlsx
+++ b/Excel Class Files/Part 8 What if Analysis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deves\Documents\GitHub\Free_Datasets\Excel Class Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4CA5928-4177-4A63-9BEC-962E91924FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133DD95F-0E7E-4C12-949D-486D23196017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="product_price">'Scenario Manager'!$B$8</definedName>
+    <definedName name="Revenue">'Scenario Manager'!$B$10</definedName>
     <definedName name="Unit_sold">'Scenario Manager'!$B$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -324,11 +325,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" textRotation="90"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -844,7 +845,7 @@
         <v>200</v>
       </c>
       <c r="D7" s="1"/>
-      <c r="E7" s="14">
+      <c r="E7" s="13">
         <f>B13</f>
         <v>10000</v>
       </c>
@@ -871,17 +872,17 @@
       <c r="B8" s="10">
         <v>500</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="15" t="s">
         <v>23</v>
       </c>
       <c r="E8" s="2">
         <v>700</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -890,27 +891,27 @@
       <c r="B9" s="10">
         <v>50000</v>
       </c>
-      <c r="D9" s="13"/>
+      <c r="D9" s="15"/>
       <c r="E9" s="2">
         <v>750</v>
       </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" s="10"/>
-      <c r="D10" s="13"/>
+      <c r="D10" s="15"/>
       <c r="E10" s="2">
         <v>800</v>
       </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
@@ -920,15 +921,15 @@
         <f>B6*B7</f>
         <v>160000</v>
       </c>
-      <c r="D11" s="13"/>
+      <c r="D11" s="15"/>
       <c r="E11" s="2">
         <v>850</v>
       </c>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
@@ -938,15 +939,15 @@
         <f>(B8*B7)+B9</f>
         <v>150000</v>
       </c>
-      <c r="D12" s="13"/>
+      <c r="D12" s="15"/>
       <c r="E12" s="2">
         <v>900</v>
       </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
